--- a/models/reports/2359_market_analysis_20260509_v2.xlsx
+++ b/models/reports/2359_market_analysis_20260509_v2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryosuke0923\ryosuke-japanese-equity-research\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\ryosuke-japanese-equity-research\models\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCB03287-B95A-4F38-BE4F-32ED04D6A02B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31BC5444-1F68-4596-9A6D-E1EDB64F2A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2920" yWindow="2920" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Implied Growth Analysis" sheetId="1" r:id="rId1"/>
@@ -18,12 +18,25 @@
     <sheet name="Market Scorecard" sheetId="3" r:id="rId3"/>
     <sheet name="Narrative Stage" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="236">
   <si>
     <t>Implied Growth Analysis - 株式会社コア (2359.T)</t>
   </si>
@@ -55,12 +68,6 @@
     <t>now</t>
   </si>
   <si>
-    <t>Entry Price</t>
-  </si>
-  <si>
-    <t>cost basis</t>
-  </si>
-  <si>
     <t>DCF Base PGM Target</t>
   </si>
   <si>
@@ -734,6 +741,10 @@
   </si>
   <si>
     <t>ファンダ的に割安 × ナラティブStage 0-1 = ダブルバガー本命ゾーン</t>
+  </si>
+  <si>
+    <t>(非公開)</t>
+    <phoneticPr fontId="7"/>
   </si>
 </sst>
 </file>
@@ -762,32 +773,38 @@
       <sz val="14"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="6"/>
@@ -926,10 +943,10 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1456,7 +1473,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:20" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="43" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="44"/>
@@ -1479,7 +1496,7 @@
       <c r="T2" s="44"/>
     </row>
     <row r="5" spans="2:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B5" s="43" t="s">
+      <c r="B5" s="45" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="44"/>
@@ -1533,30 +1550,17 @@
     </row>
     <row r="8" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="3">
-        <v>2127</v>
-      </c>
-      <c r="D8" s="3">
-        <f t="shared" si="0"/>
-        <v>30556.696827</v>
-      </c>
-      <c r="E8" s="3">
-        <f t="shared" si="1"/>
-        <v>23259.896827</v>
-      </c>
-      <c r="F8" s="3">
-        <f t="shared" si="2"/>
-        <v>23259.896827</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>11</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="2"/>
     </row>
     <row r="9" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C9" s="3">
         <v>3290.2729790835629</v>
@@ -1574,12 +1578,12 @@
         <v>39971.593935085344</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C10" s="3">
         <v>3629</v>
@@ -1597,12 +1601,12 @@
         <v>44837.780528999996</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C11" s="3">
         <v>1960</v>
@@ -1620,12 +1624,12 @@
         <v>20860.757959999999</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C12" s="3">
         <v>2330</v>
@@ -1643,12 +1647,12 @@
         <v>26176.215330000003</v>
       </c>
       <c r="G12" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="2:20" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B14" s="45" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="2:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B14" s="43" t="s">
-        <v>19</v>
       </c>
       <c r="C14" s="44"/>
       <c r="D14" s="44"/>
@@ -1671,12 +1675,12 @@
     </row>
     <row r="16" spans="2:20" ht="14" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="2:20" ht="14" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C17" s="4">
         <v>-0.5</v>
@@ -1735,12 +1739,12 @@
     </row>
     <row r="19" spans="2:20" ht="14" x14ac:dyDescent="0.3">
       <c r="B19" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C20" s="6">
         <f>C17*D56</f>
@@ -1817,7 +1821,7 @@
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C21" s="6">
         <f>C17*E56</f>
@@ -1894,7 +1898,7 @@
     </row>
     <row r="22" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C22" s="6">
         <f>C17*F56</f>
@@ -1971,7 +1975,7 @@
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C23" s="6">
         <f>C17*G56</f>
@@ -2048,7 +2052,7 @@
     </row>
     <row r="24" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C24" s="6">
         <f>C17*H56</f>
@@ -2125,7 +2129,7 @@
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C25" s="7">
         <f>C48*(1+C20)</f>
@@ -2202,7 +2206,7 @@
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C26" s="7">
         <f t="shared" ref="C26:L29" si="3">C25*(1+C21)</f>
@@ -2245,7 +2249,7 @@
         <v>29444.457199942368</v>
       </c>
       <c r="M26" s="7">
-        <f t="shared" ref="M26:V29" si="4">M25*(1+M21)</f>
+        <f t="shared" ref="M26:T29" si="4">M25*(1+M21)</f>
         <v>29944.960744949574</v>
       </c>
       <c r="N26" s="7">
@@ -2279,7 +2283,7 @@
     </row>
     <row r="27" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C27" s="7">
         <f t="shared" si="3"/>
@@ -2356,7 +2360,7 @@
     </row>
     <row r="28" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C28" s="7">
         <f t="shared" si="3"/>
@@ -2433,7 +2437,7 @@
     </row>
     <row r="29" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B29" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C29" s="7">
         <f t="shared" si="3"/>
@@ -2510,7 +2514,7 @@
     </row>
     <row r="30" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C30" s="7">
         <f>C25*(C50+C17*(D57-C50))</f>
@@ -2587,7 +2591,7 @@
     </row>
     <row r="31" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C31" s="7">
         <f>C26*(C50+C17*(E57-C50))</f>
@@ -2664,7 +2668,7 @@
     </row>
     <row r="32" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C32" s="7">
         <f>C27*(C50+C17*(F57-C50))</f>
@@ -2741,7 +2745,7 @@
     </row>
     <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C33" s="7">
         <f>C28*(C50+C17*(G57-C50))</f>
@@ -2818,7 +2822,7 @@
     </row>
     <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B34" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C34" s="7">
         <f>C29*(C50+C17*(H57-C50))</f>
@@ -2895,7 +2899,7 @@
     </row>
     <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B35" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C35" s="7">
         <f>MAX(0,C30*(1-0.3062))+D58-D59-D60</f>
@@ -2972,7 +2976,7 @@
     </row>
     <row r="36" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B36" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C36" s="7">
         <f>MAX(0,C31*(1-0.3062))+E58-E59-E60</f>
@@ -3049,7 +3053,7 @@
     </row>
     <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C37" s="7">
         <f>MAX(0,C32*(1-0.3062))+F58-F59-F60</f>
@@ -3126,7 +3130,7 @@
     </row>
     <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B38" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C38" s="7">
         <f>MAX(0,C33*(1-0.3062))+G58-G59-G60</f>
@@ -3203,7 +3207,7 @@
     </row>
     <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B39" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C39" s="7">
         <f>MAX(0,C34*(1-0.3062))+H58-H59-H60</f>
@@ -3280,7 +3284,7 @@
     </row>
     <row r="40" spans="2:20" ht="14" x14ac:dyDescent="0.3">
       <c r="B40" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C40" s="7">
         <f t="shared" ref="C40:T40" si="5">C35/(1+0.1215)^(0+0)+C36/(1+0.1215)^(0+1)+C37/(1+0.1215)^(0+2)+C38/(1+0.1215)^(0+3)+C39/(1+0.1215)^(0+4)</f>
@@ -3357,7 +3361,7 @@
     </row>
     <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B41" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C41" s="7">
         <f t="shared" ref="C41:T41" si="6">C39*(1+0.02)/(0.1215-0.02)</f>
@@ -3434,7 +3438,7 @@
     </row>
     <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B42" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C42" s="7">
         <f t="shared" ref="C42:T42" si="7">C41/(1+0.1215)^(0+4)</f>
@@ -3511,7 +3515,7 @@
     </row>
     <row r="43" spans="2:20" ht="14" x14ac:dyDescent="0.3">
       <c r="B43" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C43" s="7">
         <f t="shared" ref="C43:T43" si="8">C40+C42</f>
@@ -3588,7 +3592,7 @@
     </row>
     <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B44" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C44" s="7">
         <f t="shared" ref="C44:T44" si="9">C43--7296.8</f>
@@ -3665,7 +3669,7 @@
     </row>
     <row r="45" spans="2:20" ht="14" x14ac:dyDescent="0.3">
       <c r="B45" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C45" s="9">
         <f t="shared" ref="C45:T45" si="10">C44*1000000/14366101</f>
@@ -3741,8 +3745,8 @@
       </c>
     </row>
     <row r="47" spans="2:20" ht="14" x14ac:dyDescent="0.3">
-      <c r="B47" s="45" t="s">
-        <v>49</v>
+      <c r="B47" s="46" t="s">
+        <v>47</v>
       </c>
       <c r="C47" s="44"/>
       <c r="D47" s="44"/>
@@ -3765,7 +3769,7 @@
     </row>
     <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B48" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C48" s="7">
         <v>26530</v>
@@ -3773,7 +3777,7 @@
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B49" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C49" s="7">
         <v>3820</v>
@@ -3781,7 +3785,7 @@
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B50" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C50" s="6">
         <v>0.14398793818318881</v>
@@ -3789,27 +3793,27 @@
     </row>
     <row r="51" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="B51" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E51" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="D51" s="5" t="s">
+      <c r="F51" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E51" s="5" t="s">
+      <c r="G51" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="F51" s="5" t="s">
+      <c r="H51" s="5" t="s">
         <v>56</v>
-      </c>
-      <c r="G51" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="H51" s="5" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B52" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C52" s="7">
         <v>5084</v>
@@ -3832,7 +3836,7 @@
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B53" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C53" s="7">
         <v>13695</v>
@@ -3855,7 +3859,7 @@
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C54" s="7">
         <v>7751</v>
@@ -3878,7 +3882,7 @@
     </row>
     <row r="55" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="B55" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C55" s="7">
         <v>26530</v>
@@ -3901,7 +3905,7 @@
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B56" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D56" s="6">
         <v>9.0398416886543487E-2</v>
@@ -3921,7 +3925,7 @@
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B57" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D57" s="6">
         <v>0.1536025037100387</v>
@@ -3941,7 +3945,7 @@
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B58" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D58" s="7">
         <v>210</v>
@@ -3961,7 +3965,7 @@
     </row>
     <row r="59" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B59" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D59" s="7">
         <v>100</v>
@@ -3981,7 +3985,7 @@
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B60" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D60" s="7">
         <v>1179.09691330959</v>
@@ -4000,8 +4004,8 @@
       </c>
     </row>
     <row r="62" spans="2:8" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B62" s="43" t="s">
-        <v>68</v>
+      <c r="B62" s="45" t="s">
+        <v>66</v>
       </c>
       <c r="C62" s="44"/>
       <c r="D62" s="44"/>
@@ -4016,13 +4020,13 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F63" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="64" spans="2:8" x14ac:dyDescent="0.2">
@@ -4050,23 +4054,23 @@
     <row r="65" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B65" s="2" t="str">
         <f t="shared" si="11"/>
-        <v>Entry Price</v>
+        <v>(非公開)</v>
       </c>
       <c r="C65" s="3">
         <f t="shared" si="11"/>
-        <v>2127</v>
-      </c>
-      <c r="D65" s="10">
+        <v>0</v>
+      </c>
+      <c r="D65" s="10" t="e">
         <f t="shared" si="12"/>
-        <v>1.9950284136096799E-2</v>
-      </c>
-      <c r="E65" s="2" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="E65" s="2" t="e">
         <f t="shared" si="13"/>
-        <v>Neutral</v>
-      </c>
-      <c r="F65" s="2" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="F65" s="2" t="e">
         <f t="shared" si="14"/>
-        <v>0-50% of Base growth priced in</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="66" spans="2:7" x14ac:dyDescent="0.2">
@@ -4158,8 +4162,8 @@
       </c>
     </row>
     <row r="71" spans="2:7" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B71" s="43" t="s">
-        <v>72</v>
+      <c r="B71" s="45" t="s">
+        <v>70</v>
       </c>
       <c r="C71" s="44"/>
       <c r="D71" s="44"/>
@@ -4169,27 +4173,27 @@
     </row>
     <row r="72" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B72" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D72" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="E72" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D72" s="1" t="s">
+      <c r="F72" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="E72" s="1" t="s">
+      <c r="G72" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G72" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="73" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B73" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C73" s="11">
         <v>1</v>
@@ -4213,7 +4217,7 @@
     </row>
     <row r="74" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B74" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C74" s="11">
         <v>1.5</v>
@@ -4237,7 +4241,7 @@
     </row>
     <row r="75" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B75" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C75" s="11">
         <v>0.85</v>
@@ -4261,7 +4265,7 @@
     </row>
     <row r="76" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B76" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C76" s="11">
         <v>0.4</v>
@@ -4285,7 +4289,7 @@
     </row>
     <row r="77" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B77" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C77" s="11">
         <v>0.15</v>
@@ -4308,8 +4312,8 @@
       </c>
     </row>
     <row r="79" spans="2:7" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B79" s="43" t="s">
-        <v>84</v>
+      <c r="B79" s="45" t="s">
+        <v>82</v>
       </c>
       <c r="C79" s="44"/>
       <c r="D79" s="44"/>
@@ -4319,7 +4323,7 @@
     </row>
     <row r="80" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B80" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C80" s="10">
         <f>D64</f>
@@ -4328,7 +4332,7 @@
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B81" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C81" s="14">
         <v>1</v>
@@ -4336,7 +4340,7 @@
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B82" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C82" s="15">
         <f>C81-C80</f>
@@ -4345,7 +4349,7 @@
     </row>
     <row r="83" spans="2:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B83" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C83" s="16" t="str">
         <f>IF(C82&gt;0.5,"BUY (upside surprise expected)",IF(C82&gt;0.2,"BUY/HOLD",IF(C82&gt;=-0.2,"HOLD",IF(C82&gt;=-0.5,"HOLD/SELL","SELL (disappointment risk)"))))</f>
@@ -4354,57 +4358,57 @@
     </row>
     <row r="95" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B95" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="96" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B96" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="97" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B97" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="98" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B98" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="99" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B99" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="100" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B100" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="102" spans="2:2" ht="14" x14ac:dyDescent="0.3">
       <c r="B102" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="103" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B103" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="104" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B104" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="105" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B105" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="106" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B106" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -4434,8 +4438,8 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B2" s="46" t="s">
-        <v>100</v>
+      <c r="B2" s="43" t="s">
+        <v>98</v>
       </c>
       <c r="C2" s="44"/>
       <c r="D2" s="44"/>
@@ -4446,12 +4450,12 @@
     </row>
     <row r="3" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="B3" s="17" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B5" s="43" t="s">
-        <v>102</v>
+      <c r="B5" s="45" t="s">
+        <v>100</v>
       </c>
       <c r="C5" s="44"/>
       <c r="D5" s="44"/>
@@ -4462,7 +4466,7 @@
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C6" s="18">
         <v>2006</v>
@@ -4470,7 +4474,7 @@
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C7" s="18">
         <v>14366101</v>
@@ -4478,7 +4482,7 @@
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C8" s="19">
         <v>-7296.8</v>
@@ -4486,7 +4490,7 @@
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C9" s="18">
         <v>26530</v>
@@ -4494,15 +4498,15 @@
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C11" s="20">
         <v>0.3</v>
@@ -4510,15 +4514,15 @@
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C12" s="20">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="2:8" ht="14" x14ac:dyDescent="0.3">
-      <c r="B14" s="45" t="s">
-        <v>111</v>
+      <c r="B14" s="46" t="s">
+        <v>109</v>
       </c>
       <c r="C14" s="44"/>
       <c r="D14" s="44"/>
@@ -4529,24 +4533,24 @@
     </row>
     <row r="15" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="C15" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="E15" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="F15" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="E15" s="21" t="s">
+      <c r="G15" s="21" t="s">
         <v>114</v>
-      </c>
-      <c r="F15" s="21" t="s">
-        <v>115</v>
-      </c>
-      <c r="G15" s="21" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C16" s="22">
         <v>0.95226210264615385</v>
@@ -4566,7 +4570,7 @@
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C18" s="23">
         <f>C6*C7/1000000</f>
@@ -4584,7 +4588,7 @@
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C20" s="24">
         <f>C19/C9</f>
@@ -4593,7 +4597,7 @@
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C21" s="24" t="str">
         <f>IFERROR(C19/C10,"-")</f>
@@ -4601,8 +4605,8 @@
       </c>
     </row>
     <row r="23" spans="2:8" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B23" s="43" t="s">
-        <v>121</v>
+      <c r="B23" s="45" t="s">
+        <v>119</v>
       </c>
       <c r="C23" s="44"/>
       <c r="D23" s="44"/>
@@ -4613,7 +4617,7 @@
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C24" s="25">
         <f>C20/E16-1</f>
@@ -4622,7 +4626,7 @@
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C25" s="25">
         <f>C20/C16-1</f>
@@ -4631,7 +4635,7 @@
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C26" s="26">
         <f>(C20-E16)/(F16-D16)</f>
@@ -4640,7 +4644,7 @@
     </row>
     <row r="27" spans="2:8" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B27" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C27" s="48" t="str">
         <f>IF(C26&lt;-C12,"割安（分布下限以下）",IF(C26&lt;-C11,"やや割安",IF(C26&lt;=C11,"中立（中央値近傍）",IF(C26&lt;=C12,"やや割高","割高（分布上限以上）"))))</f>
@@ -4650,8 +4654,8 @@
       <c r="E27" s="49"/>
     </row>
     <row r="29" spans="2:8" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B29" s="43" t="s">
-        <v>126</v>
+      <c r="B29" s="45" t="s">
+        <v>124</v>
       </c>
       <c r="C29" s="44"/>
       <c r="D29" s="44"/>
@@ -4662,18 +4666,18 @@
     </row>
     <row r="30" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="C30" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C31" s="27">
         <f>C16</f>
@@ -4690,7 +4694,7 @@
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B32" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C32" s="27">
         <f>D16</f>
@@ -4707,7 +4711,7 @@
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C33" s="27">
         <f>E16</f>
@@ -4724,7 +4728,7 @@
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B34" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C34" s="27">
         <f>F16</f>
@@ -4741,7 +4745,7 @@
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C35" s="27">
         <f>G16</f>
@@ -4757,8 +4761,8 @@
       </c>
     </row>
     <row r="37" spans="2:8" ht="14" x14ac:dyDescent="0.3">
-      <c r="B37" s="45" t="s">
-        <v>130</v>
+      <c r="B37" s="46" t="s">
+        <v>128</v>
       </c>
       <c r="C37" s="44"/>
       <c r="D37" s="44"/>
@@ -4769,7 +4773,7 @@
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B38" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C38" s="22">
         <v>1.6916825714965911</v>
@@ -4777,7 +4781,7 @@
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B39" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C39" s="22">
         <v>1.0360113772577699</v>
@@ -4785,7 +4789,7 @@
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B40" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C40" s="22">
         <v>0.95226210264615385</v>
@@ -4793,7 +4797,7 @@
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B41" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C41" s="22">
         <v>1.1261890080000001</v>
@@ -4801,15 +4805,15 @@
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B42" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C42" s="22">
         <v>3.289091671148936</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B45" s="43" t="s">
-        <v>136</v>
+      <c r="B45" s="45" t="s">
+        <v>134</v>
       </c>
       <c r="C45" s="44"/>
       <c r="D45" s="44"/>
@@ -4820,7 +4824,7 @@
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B46" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C46" s="19">
         <v>2207</v>
@@ -4828,15 +4832,15 @@
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B47" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B48" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C48" s="27">
         <f>IFERROR(C18/C46,"n/a")</f>
@@ -4845,7 +4849,7 @@
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B49" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C49" s="27" t="str">
         <f>IFERROR(C19/C47,"n/a")</f>
@@ -4854,7 +4858,7 @@
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B51" s="47" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C51" s="44"/>
       <c r="D51" s="44"/>
@@ -4865,7 +4869,7 @@
     </row>
     <row r="52" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B52" s="50" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C52" s="44"/>
       <c r="D52" s="44"/>
@@ -4907,8 +4911,8 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B2" s="46" t="s">
-        <v>143</v>
+      <c r="B2" s="43" t="s">
+        <v>141</v>
       </c>
       <c r="C2" s="44"/>
       <c r="D2" s="44"/>
@@ -4917,8 +4921,8 @@
       <c r="G2" s="44"/>
     </row>
     <row r="5" spans="2:7" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B5" s="43" t="s">
-        <v>144</v>
+      <c r="B5" s="45" t="s">
+        <v>142</v>
       </c>
       <c r="C5" s="44"/>
       <c r="D5" s="44"/>
@@ -4928,27 +4932,27 @@
     </row>
     <row r="6" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>149</v>
-      </c>
       <c r="G6" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C7" s="10">
         <f>1-'Implied Growth Analysis'!C80</f>
@@ -4972,7 +4976,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C8" s="31">
         <f>IFERROR((C19-C20)/C20,0)</f>
@@ -4996,7 +5000,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C9" s="11">
         <f>IFERROR(C34/C33,0)</f>
@@ -5020,7 +5024,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C10" s="31">
         <f>AVERAGE(E44:E45)</f>
@@ -5044,7 +5048,7 @@
     </row>
     <row r="12" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B12" s="32" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -5059,8 +5063,8 @@
       </c>
     </row>
     <row r="17" spans="2:7" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B17" s="43" t="s">
-        <v>155</v>
+      <c r="B17" s="45" t="s">
+        <v>153</v>
       </c>
       <c r="C17" s="44"/>
       <c r="D17" s="44"/>
@@ -5078,7 +5082,7 @@
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C20" s="18">
         <v>1964</v>
@@ -5086,7 +5090,7 @@
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C21" s="18">
         <v>2330</v>
@@ -5094,7 +5098,7 @@
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C22" s="18">
         <v>2330</v>
@@ -5102,7 +5106,7 @@
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C23" s="18">
         <v>1960</v>
@@ -5110,12 +5114,12 @@
     </row>
     <row r="25" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B25" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C26" s="35">
         <f>IFERROR((C19-C20)/C20,"")</f>
@@ -5124,7 +5128,7 @@
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C27" s="35">
         <f>IFERROR((C19-C21)/C21,"")</f>
@@ -5133,7 +5137,7 @@
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C28" s="35">
         <f>IFERROR((C19-C22)/C22,"")</f>
@@ -5141,8 +5145,8 @@
       </c>
     </row>
     <row r="31" spans="2:7" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B31" s="43" t="s">
-        <v>162</v>
+      <c r="B31" s="45" t="s">
+        <v>160</v>
       </c>
       <c r="C31" s="44"/>
       <c r="D31" s="44"/>
@@ -5152,7 +5156,7 @@
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B33" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C33" s="18">
         <v>50000</v>
@@ -5160,7 +5164,7 @@
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C34" s="18">
         <v>5100</v>
@@ -5168,7 +5172,7 @@
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C35" s="18">
         <v>169300</v>
@@ -5176,7 +5180,7 @@
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B36" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C36" s="26">
         <f>IFERROR(C33/C34,99)</f>
@@ -5185,7 +5189,7 @@
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B37" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C37" s="26">
         <f>IFERROR(C34/C35,0)</f>
@@ -5193,8 +5197,8 @@
       </c>
     </row>
     <row r="41" spans="2:7" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B41" s="43" t="s">
-        <v>168</v>
+      <c r="B41" s="45" t="s">
+        <v>166</v>
       </c>
       <c r="C41" s="44"/>
       <c r="D41" s="44"/>
@@ -5204,24 +5208,24 @@
     </row>
     <row r="43" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B43" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D43" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="E43" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="F43" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B44" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C44" s="36">
         <v>0.16320803664921479</v>
@@ -5240,7 +5244,7 @@
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B45" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C45" s="36">
         <v>9.0398416886543487E-2</v>
@@ -5258,8 +5262,8 @@
       </c>
     </row>
     <row r="53" spans="2:7" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B53" s="43" t="s">
-        <v>176</v>
+      <c r="B53" s="45" t="s">
+        <v>174</v>
       </c>
       <c r="C53" s="44"/>
       <c r="D53" s="44"/>
@@ -5269,10 +5273,10 @@
     </row>
     <row r="55" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B55" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C55" s="50" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D55" s="44"/>
       <c r="E55" s="44"/>
@@ -5281,10 +5285,10 @@
     </row>
     <row r="56" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B56" s="5" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C56" s="50" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D56" s="44"/>
       <c r="E56" s="44"/>
@@ -5293,10 +5297,10 @@
     </row>
     <row r="57" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B57" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C57" s="50" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D57" s="44"/>
       <c r="E57" s="44"/>
@@ -5305,10 +5309,10 @@
     </row>
     <row r="58" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B58" s="5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C58" s="50" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D58" s="44"/>
       <c r="E58" s="44"/>
@@ -5317,10 +5321,10 @@
     </row>
     <row r="59" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B59" s="5" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C59" s="50" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D59" s="44"/>
       <c r="E59" s="44"/>
@@ -5329,27 +5333,27 @@
     </row>
     <row r="62" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B62" s="5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="63" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B63" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="64" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B64" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="65" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B65" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="66" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B66" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -5389,8 +5393,8 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B2" s="46" t="s">
-        <v>192</v>
+      <c r="B2" s="43" t="s">
+        <v>190</v>
       </c>
       <c r="C2" s="44"/>
       <c r="D2" s="44"/>
@@ -5399,12 +5403,12 @@
     </row>
     <row r="3" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="B3" s="17" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B5" s="43" t="s">
-        <v>194</v>
+      <c r="B5" s="45" t="s">
+        <v>192</v>
       </c>
       <c r="C5" s="44"/>
       <c r="D5" s="44"/>
@@ -5413,33 +5417,33 @@
     </row>
     <row r="6" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="G6" t="s">
         <v>195</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="G6" t="s">
-        <v>197</v>
-      </c>
       <c r="H6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C7" s="38">
         <v>1</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G7" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -5447,16 +5451,16 @@
     </row>
     <row r="8" spans="2:8" ht="26" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C8" s="38">
         <v>2</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G8" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H8">
         <v>2</v>
@@ -5464,16 +5468,16 @@
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C9" s="38">
         <v>1</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -5481,16 +5485,16 @@
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C10" s="38">
         <v>1</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G10" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -5498,16 +5502,16 @@
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C11" s="38">
         <v>1</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G11" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -5515,16 +5519,16 @@
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C12" s="38">
         <v>2</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G12" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="H12">
         <v>2</v>
@@ -5532,15 +5536,15 @@
     </row>
     <row r="13" spans="2:8" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B13" s="5" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C13" s="40">
         <v>8</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B15" s="43" t="s">
-        <v>217</v>
+      <c r="B15" s="45" t="s">
+        <v>215</v>
       </c>
       <c r="C15" s="44"/>
       <c r="D15" s="44"/>
@@ -5549,10 +5553,10 @@
     </row>
     <row r="16" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="B16" s="5" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C16" s="51" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D16" s="44"/>
       <c r="E16" s="44"/>
@@ -5560,10 +5564,10 @@
     </row>
     <row r="17" spans="2:6" ht="14" x14ac:dyDescent="0.3">
       <c r="B17" s="5" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C17" s="51" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D17" s="44"/>
       <c r="E17" s="44"/>
@@ -5571,10 +5575,10 @@
     </row>
     <row r="18" spans="2:6" ht="14" x14ac:dyDescent="0.3">
       <c r="B18" s="5" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C18" s="51" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D18" s="44"/>
       <c r="E18" s="44"/>
@@ -5582,18 +5586,18 @@
     </row>
     <row r="19" spans="2:6" ht="14" x14ac:dyDescent="0.3">
       <c r="B19" s="5" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C19" s="51" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D19" s="44"/>
       <c r="E19" s="44"/>
       <c r="F19" s="44"/>
     </row>
     <row r="21" spans="2:6" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B21" s="43" t="s">
-        <v>226</v>
+      <c r="B21" s="45" t="s">
+        <v>224</v>
       </c>
       <c r="C21" s="44"/>
       <c r="D21" s="44"/>
@@ -5602,31 +5606,31 @@
     </row>
     <row r="22" spans="2:6" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B22" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="C22" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="D22" s="44" t="s">
         <v>227</v>
-      </c>
-      <c r="C22" s="41" t="s">
-        <v>228</v>
-      </c>
-      <c r="D22" s="44" t="s">
-        <v>229</v>
       </c>
       <c r="E22" s="44"/>
       <c r="F22" s="44"/>
     </row>
     <row r="23" spans="2:6" ht="14" x14ac:dyDescent="0.3">
       <c r="B23" s="5" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C23" s="50" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D23" s="44"/>
       <c r="E23" s="44"/>
       <c r="F23" s="44"/>
     </row>
     <row r="25" spans="2:6" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B25" s="43" t="s">
-        <v>232</v>
+      <c r="B25" s="45" t="s">
+        <v>230</v>
       </c>
       <c r="C25" s="44"/>
       <c r="D25" s="44"/>
@@ -5635,7 +5639,7 @@
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B26" s="50" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C26" s="44"/>
       <c r="D26" s="44"/>
@@ -5643,8 +5647,8 @@
       <c r="F26" s="44"/>
     </row>
     <row r="28" spans="2:6" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B28" s="43" t="s">
-        <v>234</v>
+      <c r="B28" s="45" t="s">
+        <v>232</v>
       </c>
       <c r="C28" s="44"/>
       <c r="D28" s="44"/>
@@ -5653,19 +5657,20 @@
     </row>
     <row r="29" spans="2:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B29" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C29" s="42" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D29" s="50" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E29" s="44"/>
       <c r="F29" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="D29:F29"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B25:F25"/>
@@ -5679,7 +5684,6 @@
     <mergeCell ref="C18:F18"/>
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="C23:F23"/>
-    <mergeCell ref="D29:F29"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
